--- a/StructureDefinition-ng-patient.xlsx
+++ b/StructureDefinition-ng-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8827" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8827" uniqueCount="903">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:22:49+01:00</t>
+    <t>2026-08-17T07:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1080,7 +1080,10 @@
     <t>Patient.identifier:NationalIDNo.system</t>
   </si>
   <si>
-    <t>NIMC's identifier in the system autheticated to https://nimc.org/nin</t>
+    <t>NamingSystem for NIMC's identifier in the system autheticated later, maybe at https://nimc.org/nin</t>
+  </si>
+  <si>
+    <t>https://fhir-ig.digitalhealth.gov.ng/identifier/nin</t>
   </si>
   <si>
     <t>Patient.identifier:NationalIDNo.value</t>
@@ -1239,6 +1242,9 @@
     <t>The URI system identifying the authority that assigns the birth certificate number validated at http://npc.gov.ng/birthCertificate-no.</t>
   </si>
   <si>
+    <t>https://fhir-ig.digitalhealth.gov.ng/identifier/birth-cert</t>
+  </si>
+  <si>
     <t>Patient.identifier:BirthCertificateNo.value</t>
   </si>
   <si>
@@ -1314,7 +1320,10 @@
     <t>The provider of the phone number (e.g., MTN)</t>
   </si>
   <si>
-    <t>The URI system identifying the provider of the phone number validated at http://mtnonline.com/phone-no.</t>
+    <t>The URI system identifying the provider of the phone number.</t>
+  </si>
+  <si>
+    <t>https://fhir-ig.digitalhealth.gov.ng/identifier/mobile</t>
   </si>
   <si>
     <t>Patient.identifier:PhoneNumber.value</t>
@@ -1393,6 +1402,9 @@
   </si>
   <si>
     <t>The URI system identifying the provider of the insurance number validated at http://nhia.gov.ng/insurance-no.</t>
+  </si>
+  <si>
+    <t>https://fhir-ig.digitalhealth.gov.ng/identifier/ins</t>
   </si>
   <si>
     <t>Patient.identifier:InsuranceNumber.value</t>
@@ -8249,7 +8261,7 @@
         <v>85</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>237</v>
@@ -8320,7 +8332,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>241</v>
@@ -8349,7 +8361,7 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>243</v>
@@ -8437,7 +8449,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>249</v>
@@ -8552,7 +8564,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>256</v>
@@ -8669,13 +8681,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
@@ -8788,7 +8800,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>210</v>
@@ -8903,7 +8915,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>211</v>
@@ -9020,7 +9032,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>212</v>
@@ -9139,7 +9151,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>222</v>
@@ -9256,7 +9268,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>273</v>
@@ -9371,7 +9383,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>275</v>
@@ -9488,7 +9500,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>277</v>
@@ -9607,7 +9619,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>286</v>
@@ -9722,7 +9734,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>288</v>
@@ -9839,7 +9851,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>290</v>
@@ -9958,7 +9970,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>300</v>
@@ -10075,7 +10087,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>308</v>
@@ -10121,7 +10133,7 @@
         <v>85</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>85</v>
@@ -10192,7 +10204,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>317</v>
@@ -10238,7 +10250,7 @@
         <v>85</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>85</v>
@@ -10309,7 +10321,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>326</v>
@@ -10428,7 +10440,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>336</v>
@@ -10547,7 +10559,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>232</v>
@@ -10576,10 +10588,10 @@
         <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>235</v>
@@ -10666,7 +10678,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>241</v>
@@ -10695,7 +10707,7 @@
         <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>243</v>
@@ -10783,7 +10795,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>249</v>
@@ -10898,7 +10910,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>256</v>
@@ -11015,13 +11027,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>85</v>
@@ -11134,7 +11146,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>210</v>
@@ -11249,7 +11261,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>211</v>
@@ -11366,7 +11378,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>212</v>
@@ -11485,7 +11497,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>222</v>
@@ -11602,7 +11614,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>273</v>
@@ -11717,7 +11729,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>275</v>
@@ -11834,7 +11846,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>277</v>
@@ -11953,7 +11965,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>286</v>
@@ -12068,7 +12080,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>288</v>
@@ -12185,7 +12197,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>290</v>
@@ -12304,7 +12316,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>300</v>
@@ -12421,7 +12433,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>308</v>
@@ -12467,7 +12479,7 @@
         <v>85</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>85</v>
@@ -12538,7 +12550,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>317</v>
@@ -12584,7 +12596,7 @@
         <v>85</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>85</v>
@@ -12655,7 +12667,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>326</v>
@@ -12774,7 +12786,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>336</v>
@@ -12893,7 +12905,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>232</v>
@@ -12922,10 +12934,10 @@
         <v>135</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>235</v>
@@ -12941,7 +12953,7 @@
         <v>85</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>237</v>
@@ -13012,7 +13024,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>241</v>
@@ -13041,7 +13053,7 @@
         <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>243</v>
@@ -13129,7 +13141,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>249</v>
@@ -13244,7 +13256,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>256</v>
@@ -13361,13 +13373,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>85</v>
@@ -13480,7 +13492,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>210</v>
@@ -13595,7 +13607,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>211</v>
@@ -13712,7 +13724,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>212</v>
@@ -13831,7 +13843,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>222</v>
@@ -13948,7 +13960,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>273</v>
@@ -14063,7 +14075,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>275</v>
@@ -14180,7 +14192,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>277</v>
@@ -14299,7 +14311,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>286</v>
@@ -14414,7 +14426,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>288</v>
@@ -14531,7 +14543,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>290</v>
@@ -14650,7 +14662,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>300</v>
@@ -14767,7 +14779,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>308</v>
@@ -14813,7 +14825,7 @@
         <v>85</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>85</v>
@@ -14884,7 +14896,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>317</v>
@@ -14930,7 +14942,7 @@
         <v>85</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>85</v>
@@ -15001,7 +15013,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>326</v>
@@ -15120,7 +15132,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>336</v>
@@ -15239,7 +15251,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>232</v>
@@ -15268,10 +15280,10 @@
         <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>235</v>
@@ -15287,7 +15299,7 @@
         <v>85</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>85</v>
+        <v>426</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>237</v>
@@ -15358,7 +15370,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>241</v>
@@ -15387,7 +15399,7 @@
         <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>243</v>
@@ -15475,7 +15487,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>249</v>
@@ -15590,7 +15602,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>256</v>
@@ -15707,13 +15719,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>85</v>
@@ -15826,7 +15838,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>210</v>
@@ -15941,7 +15953,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>211</v>
@@ -16058,7 +16070,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>212</v>
@@ -16177,7 +16189,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>222</v>
@@ -16294,7 +16306,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>273</v>
@@ -16409,7 +16421,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>275</v>
@@ -16526,7 +16538,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>277</v>
@@ -16645,7 +16657,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>286</v>
@@ -16760,7 +16772,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>288</v>
@@ -16877,7 +16889,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>290</v>
@@ -16996,7 +17008,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>300</v>
@@ -17113,7 +17125,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>308</v>
@@ -17159,7 +17171,7 @@
         <v>85</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>85</v>
@@ -17230,7 +17242,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>317</v>
@@ -17276,7 +17288,7 @@
         <v>85</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>85</v>
@@ -17347,7 +17359,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>326</v>
@@ -17466,7 +17478,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>336</v>
@@ -17585,7 +17597,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>232</v>
@@ -17614,10 +17626,10 @@
         <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>235</v>
@@ -17633,7 +17645,7 @@
         <v>85</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>237</v>
@@ -17704,7 +17716,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>241</v>
@@ -17733,7 +17745,7 @@
         <v>107</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>243</v>
@@ -17821,7 +17833,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>249</v>
@@ -17936,7 +17948,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>256</v>
@@ -18053,13 +18065,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>85</v>
@@ -18172,7 +18184,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>210</v>
@@ -18287,7 +18299,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>211</v>
@@ -18404,7 +18416,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>212</v>
@@ -18523,7 +18535,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>222</v>
@@ -18640,7 +18652,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>273</v>
@@ -18755,7 +18767,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>275</v>
@@ -18872,7 +18884,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>277</v>
@@ -18991,7 +19003,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>286</v>
@@ -19106,7 +19118,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>288</v>
@@ -19223,7 +19235,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>290</v>
@@ -19342,7 +19354,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>300</v>
@@ -19459,7 +19471,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>308</v>
@@ -19505,7 +19517,7 @@
         <v>85</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>85</v>
@@ -19576,7 +19588,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>317</v>
@@ -19622,7 +19634,7 @@
         <v>85</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>85</v>
@@ -19693,7 +19705,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>326</v>
@@ -19812,7 +19824,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>336</v>
@@ -19931,7 +19943,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>232</v>
@@ -19960,10 +19972,10 @@
         <v>135</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>235</v>
@@ -20050,7 +20062,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>241</v>
@@ -20079,7 +20091,7 @@
         <v>107</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>243</v>
@@ -20167,7 +20179,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>249</v>
@@ -20282,7 +20294,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>256</v>
@@ -20399,10 +20411,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20428,67 +20440,67 @@
         <v>327</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="O148" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q148" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="R148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>83</v>
@@ -20503,13 +20515,13 @@
         <v>105</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>111</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>85</v>
@@ -20520,10 +20532,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20546,19 +20558,19 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>85</v>
@@ -20607,7 +20619,7 @@
         <v>85</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>83</v>
@@ -20622,16 +20634,16 @@
         <v>105</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>85</v>
@@ -20639,10 +20651,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20754,10 +20766,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20871,10 +20883,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20900,16 +20912,16 @@
         <v>169</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>85</v>
@@ -20937,10 +20949,10 @@
         <v>217</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>85</v>
@@ -20958,7 +20970,7 @@
         <v>85</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>83</v>
@@ -20973,7 +20985,7 @@
         <v>105</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>85</v>
@@ -20982,7 +20994,7 @@
         <v>85</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>85</v>
@@ -20990,10 +21002,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21019,16 +21031,16 @@
         <v>107</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>85</v>
@@ -21077,7 +21089,7 @@
         <v>85</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -21092,7 +21104,7 @@
         <v>105</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>85</v>
@@ -21101,7 +21113,7 @@
         <v>85</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>85</v>
@@ -21109,14 +21121,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -21138,13 +21150,13 @@
         <v>107</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21194,7 +21206,7 @@
         <v>85</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>83</v>
@@ -21209,7 +21221,7 @@
         <v>105</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>85</v>
@@ -21218,7 +21230,7 @@
         <v>85</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>85</v>
@@ -21226,14 +21238,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21255,13 +21267,13 @@
         <v>107</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21311,7 +21323,7 @@
         <v>85</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>83</v>
@@ -21326,7 +21338,7 @@
         <v>105</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>85</v>
@@ -21335,7 +21347,7 @@
         <v>85</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>85</v>
@@ -21343,10 +21355,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21372,10 +21384,10 @@
         <v>107</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21426,7 +21438,7 @@
         <v>85</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>83</v>
@@ -21441,7 +21453,7 @@
         <v>105</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>85</v>
@@ -21450,7 +21462,7 @@
         <v>85</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>85</v>
@@ -21458,10 +21470,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21487,10 +21499,10 @@
         <v>107</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21541,7 +21553,7 @@
         <v>85</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>83</v>
@@ -21556,7 +21568,7 @@
         <v>105</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>85</v>
@@ -21565,7 +21577,7 @@
         <v>85</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>85</v>
@@ -21573,10 +21585,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21602,14 +21614,14 @@
         <v>250</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>85</v>
@@ -21658,7 +21670,7 @@
         <v>85</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
@@ -21673,7 +21685,7 @@
         <v>105</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>85</v>
@@ -21682,7 +21694,7 @@
         <v>85</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>85</v>
@@ -21690,10 +21702,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21716,19 +21728,19 @@
         <v>94</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>85</v>
@@ -21777,7 +21789,7 @@
         <v>85</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>83</v>
@@ -21792,16 +21804,16 @@
         <v>105</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>85</v>
@@ -21809,10 +21821,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21838,16 +21850,16 @@
         <v>169</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>85</v>
@@ -21876,7 +21888,7 @@
       </c>
       <c r="Y160" s="2"/>
       <c r="Z160" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>85</v>
@@ -21894,7 +21906,7 @@
         <v>85</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>83</v>
@@ -21909,16 +21921,16 @@
         <v>105</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>85</v>
@@ -21926,10 +21938,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21952,19 +21964,19 @@
         <v>94</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>85</v>
@@ -22013,7 +22025,7 @@
         <v>85</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>83</v>
@@ -22028,27 +22040,27 @@
         <v>105</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22071,19 +22083,19 @@
         <v>94</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>85</v>
@@ -22132,7 +22144,7 @@
         <v>85</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>83</v>
@@ -22147,7 +22159,7 @@
         <v>105</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>111</v>
@@ -22156,7 +22168,7 @@
         <v>85</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>85</v>
@@ -22164,10 +22176,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22190,19 +22202,19 @@
         <v>94</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>85</v>
@@ -22251,7 +22263,7 @@
         <v>85</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>83</v>
@@ -22266,16 +22278,16 @@
         <v>105</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>85</v>
@@ -22283,10 +22295,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22398,10 +22410,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22515,13 +22527,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>85</v>
@@ -22543,13 +22555,13 @@
         <v>85</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22632,10 +22644,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22661,16 +22673,16 @@
         <v>169</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>85</v>
@@ -22683,7 +22695,7 @@
         <v>85</v>
       </c>
       <c r="T167" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="U167" t="s" s="2">
         <v>85</v>
@@ -22698,10 +22710,10 @@
         <v>217</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>85</v>
@@ -22719,7 +22731,7 @@
         <v>85</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>83</v>
@@ -22734,7 +22746,7 @@
         <v>105</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>85</v>
@@ -22743,7 +22755,7 @@
         <v>85</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>85</v>
@@ -22751,10 +22763,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22780,13 +22792,13 @@
         <v>169</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22800,7 +22812,7 @@
         <v>85</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>85</v>
@@ -22815,10 +22827,10 @@
         <v>217</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>85</v>
@@ -22836,7 +22848,7 @@
         <v>85</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -22851,7 +22863,7 @@
         <v>105</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>85</v>
@@ -22860,7 +22872,7 @@
         <v>85</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>85</v>
@@ -22868,10 +22880,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22897,16 +22909,16 @@
         <v>107</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>85</v>
@@ -22919,7 +22931,7 @@
         <v>85</v>
       </c>
       <c r="T169" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="U169" t="s" s="2">
         <v>85</v>
@@ -22955,7 +22967,7 @@
         <v>85</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>83</v>
@@ -22970,7 +22982,7 @@
         <v>105</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>85</v>
@@ -22979,7 +22991,7 @@
         <v>85</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>85</v>
@@ -22987,10 +22999,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23016,10 +23028,10 @@
         <v>107</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23034,7 +23046,7 @@
         <v>85</v>
       </c>
       <c r="T170" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="U170" t="s" s="2">
         <v>85</v>
@@ -23070,7 +23082,7 @@
         <v>85</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -23085,7 +23097,7 @@
         <v>105</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>85</v>
@@ -23094,7 +23106,7 @@
         <v>85</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>85</v>
@@ -23102,14 +23114,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -23131,10 +23143,10 @@
         <v>107</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23149,7 +23161,7 @@
         <v>85</v>
       </c>
       <c r="T171" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="U171" t="s" s="2">
         <v>85</v>
@@ -23185,7 +23197,7 @@
         <v>85</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -23200,7 +23212,7 @@
         <v>105</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>85</v>
@@ -23209,7 +23221,7 @@
         <v>85</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>85</v>
@@ -23217,14 +23229,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -23246,13 +23258,13 @@
         <v>107</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23266,7 +23278,7 @@
         <v>85</v>
       </c>
       <c r="T172" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="U172" t="s" s="2">
         <v>85</v>
@@ -23282,7 +23294,7 @@
       </c>
       <c r="Y172" s="2"/>
       <c r="Z172" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>85</v>
@@ -23300,7 +23312,7 @@
         <v>85</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -23315,7 +23327,7 @@
         <v>105</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>85</v>
@@ -23324,7 +23336,7 @@
         <v>85</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>85</v>
@@ -23332,14 +23344,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23361,10 +23373,10 @@
         <v>107</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23395,7 +23407,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>85</v>
@@ -23413,7 +23425,7 @@
         <v>85</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
@@ -23428,7 +23440,7 @@
         <v>105</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>85</v>
@@ -23437,7 +23449,7 @@
         <v>85</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>85</v>
@@ -23445,14 +23457,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -23474,10 +23486,10 @@
         <v>107</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -23492,7 +23504,7 @@
         <v>85</v>
       </c>
       <c r="T174" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="U174" t="s" s="2">
         <v>85</v>
@@ -23528,7 +23540,7 @@
         <v>85</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>83</v>
@@ -23543,7 +23555,7 @@
         <v>105</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>85</v>
@@ -23552,7 +23564,7 @@
         <v>85</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>85</v>
@@ -23560,10 +23572,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23589,13 +23601,13 @@
         <v>107</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23645,7 +23657,7 @@
         <v>85</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>83</v>
@@ -23660,7 +23672,7 @@
         <v>105</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>85</v>
@@ -23669,7 +23681,7 @@
         <v>85</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>85</v>
@@ -23677,10 +23689,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23706,14 +23718,14 @@
         <v>250</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>85</v>
@@ -23726,7 +23738,7 @@
         <v>85</v>
       </c>
       <c r="T176" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="U176" t="s" s="2">
         <v>85</v>
@@ -23762,7 +23774,7 @@
         <v>85</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>83</v>
@@ -23777,7 +23789,7 @@
         <v>105</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>85</v>
@@ -23786,7 +23798,7 @@
         <v>85</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>85</v>
@@ -23794,10 +23806,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23823,14 +23835,14 @@
         <v>223</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>85</v>
@@ -23858,28 +23870,28 @@
         <v>151</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF177" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -23894,16 +23906,16 @@
         <v>105</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>85</v>
@@ -23911,10 +23923,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23937,19 +23949,19 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>85</v>
@@ -23998,7 +24010,7 @@
         <v>85</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>83</v>
@@ -24013,7 +24025,7 @@
         <v>105</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>111</v>
@@ -24022,7 +24034,7 @@
         <v>85</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>85</v>
@@ -24030,10 +24042,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24056,19 +24068,19 @@
         <v>85</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>85</v>
@@ -24117,7 +24129,7 @@
         <v>85</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>83</v>
@@ -24132,7 +24144,7 @@
         <v>105</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>111</v>
@@ -24141,7 +24153,7 @@
         <v>85</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>85</v>
@@ -24149,10 +24161,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24175,19 +24187,19 @@
         <v>85</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>85</v>
@@ -24236,7 +24248,7 @@
         <v>85</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>83</v>
@@ -24248,10 +24260,10 @@
         <v>85</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>111</v>
@@ -24268,10 +24280,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24383,10 +24395,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24500,10 +24512,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24583,7 +24595,7 @@
         <v>85</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>83</v>
@@ -24615,10 +24627,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24644,14 +24656,14 @@
         <v>223</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>85</v>
@@ -24679,28 +24691,28 @@
         <v>151</v>
       </c>
       <c r="Y184" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF184" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -24715,7 +24727,7 @@
         <v>105</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>111</v>
@@ -24724,7 +24736,7 @@
         <v>85</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>85</v>
@@ -24732,10 +24744,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24847,10 +24859,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24964,10 +24976,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25083,10 +25095,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25112,7 +25124,7 @@
         <v>107</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="M188" t="s" s="2">
         <v>338</v>
@@ -25150,7 +25162,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>85</v>
@@ -25200,10 +25212,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25226,17 +25238,17 @@
         <v>85</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>85</v>
@@ -25285,7 +25297,7 @@
         <v>85</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>83</v>
@@ -25300,7 +25312,7 @@
         <v>105</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>111</v>
@@ -25309,7 +25321,7 @@
         <v>85</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>85</v>
@@ -25317,10 +25329,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25432,10 +25444,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25549,10 +25561,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25578,16 +25590,16 @@
         <v>169</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>85</v>
@@ -25615,10 +25627,10 @@
         <v>217</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>85</v>
@@ -25636,7 +25648,7 @@
         <v>85</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>83</v>
@@ -25651,7 +25663,7 @@
         <v>105</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>85</v>
@@ -25660,7 +25672,7 @@
         <v>85</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>85</v>
@@ -25668,10 +25680,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25697,16 +25709,16 @@
         <v>107</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>85</v>
@@ -25755,7 +25767,7 @@
         <v>85</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>83</v>
@@ -25770,7 +25782,7 @@
         <v>105</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>85</v>
@@ -25779,7 +25791,7 @@
         <v>85</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>85</v>
@@ -25787,14 +25799,14 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -25816,13 +25828,13 @@
         <v>107</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -25872,7 +25884,7 @@
         <v>85</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>83</v>
@@ -25887,7 +25899,7 @@
         <v>105</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>85</v>
@@ -25896,7 +25908,7 @@
         <v>85</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>85</v>
@@ -25904,14 +25916,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -25933,13 +25945,13 @@
         <v>107</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -25989,7 +26001,7 @@
         <v>85</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>83</v>
@@ -26004,7 +26016,7 @@
         <v>105</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>85</v>
@@ -26013,7 +26025,7 @@
         <v>85</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>85</v>
@@ -26021,10 +26033,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26050,10 +26062,10 @@
         <v>107</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26104,7 +26116,7 @@
         <v>85</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>83</v>
@@ -26119,7 +26131,7 @@
         <v>105</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>85</v>
@@ -26128,7 +26140,7 @@
         <v>85</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>85</v>
@@ -26136,10 +26148,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26165,10 +26177,10 @@
         <v>107</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26219,7 +26231,7 @@
         <v>85</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>83</v>
@@ -26234,7 +26246,7 @@
         <v>105</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>85</v>
@@ -26243,7 +26255,7 @@
         <v>85</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>85</v>
@@ -26251,10 +26263,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26280,14 +26292,14 @@
         <v>250</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>85</v>
@@ -26336,7 +26348,7 @@
         <v>85</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>83</v>
@@ -26351,7 +26363,7 @@
         <v>105</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL198" t="s" s="2">
         <v>85</v>
@@ -26360,7 +26372,7 @@
         <v>85</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>85</v>
@@ -26368,10 +26380,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26394,19 +26406,19 @@
         <v>85</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>85</v>
@@ -26455,7 +26467,7 @@
         <v>85</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>83</v>
@@ -26470,7 +26482,7 @@
         <v>105</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AL199" t="s" s="2">
         <v>111</v>
@@ -26479,7 +26491,7 @@
         <v>85</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>85</v>
@@ -26487,10 +26499,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26602,10 +26614,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26719,10 +26731,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26748,10 +26760,10 @@
         <v>169</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -26781,10 +26793,10 @@
         <v>217</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>85</v>
@@ -26802,7 +26814,7 @@
         <v>85</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>83</v>
@@ -26811,13 +26823,13 @@
         <v>93</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>85</v>
@@ -26826,7 +26838,7 @@
         <v>85</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>85</v>
@@ -26834,10 +26846,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26863,16 +26875,16 @@
         <v>107</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>85</v>
@@ -26921,7 +26933,7 @@
         <v>85</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>83</v>
@@ -26936,7 +26948,7 @@
         <v>105</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>85</v>
@@ -26945,7 +26957,7 @@
         <v>85</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>85</v>
@@ -26953,10 +26965,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26982,16 +26994,16 @@
         <v>169</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>85</v>
@@ -27019,10 +27031,10 @@
         <v>217</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>85</v>
@@ -27040,7 +27052,7 @@
         <v>85</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>83</v>
@@ -27055,7 +27067,7 @@
         <v>105</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>85</v>
@@ -27064,7 +27076,7 @@
         <v>85</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>85</v>
@@ -27072,10 +27084,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27098,16 +27110,16 @@
         <v>94</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27157,7 +27169,7 @@
         <v>85</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>83</v>
@@ -27189,10 +27201,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27218,10 +27230,10 @@
         <v>250</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -27272,7 +27284,7 @@
         <v>85</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>83</v>
@@ -27287,7 +27299,7 @@
         <v>105</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>85</v>
@@ -27304,10 +27316,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27330,17 +27342,17 @@
         <v>85</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>85</v>
@@ -27389,7 +27401,7 @@
         <v>85</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>83</v>
@@ -27404,7 +27416,7 @@
         <v>105</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>111</v>
@@ -27413,7 +27425,7 @@
         <v>85</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>85</v>
@@ -27421,10 +27433,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27536,10 +27548,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27653,13 +27665,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D210" t="s" s="2">
         <v>85</v>
@@ -27681,13 +27693,13 @@
         <v>85</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -27770,10 +27782,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27799,16 +27811,16 @@
         <v>169</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>85</v>
@@ -27821,7 +27833,7 @@
         <v>85</v>
       </c>
       <c r="T211" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="U211" t="s" s="2">
         <v>85</v>
@@ -27836,10 +27848,10 @@
         <v>217</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>85</v>
@@ -27857,7 +27869,7 @@
         <v>85</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>83</v>
@@ -27872,7 +27884,7 @@
         <v>105</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>85</v>
@@ -27881,7 +27893,7 @@
         <v>85</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>85</v>
@@ -27889,10 +27901,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27918,13 +27930,13 @@
         <v>169</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -27938,7 +27950,7 @@
         <v>85</v>
       </c>
       <c r="T212" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="U212" t="s" s="2">
         <v>85</v>
@@ -27953,10 +27965,10 @@
         <v>217</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>85</v>
@@ -27974,7 +27986,7 @@
         <v>85</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>83</v>
@@ -27989,7 +28001,7 @@
         <v>105</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>85</v>
@@ -27998,7 +28010,7 @@
         <v>85</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>85</v>
@@ -28006,10 +28018,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28035,16 +28047,16 @@
         <v>107</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>85</v>
@@ -28057,7 +28069,7 @@
         <v>85</v>
       </c>
       <c r="T213" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="U213" t="s" s="2">
         <v>85</v>
@@ -28093,7 +28105,7 @@
         <v>85</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>83</v>
@@ -28108,7 +28120,7 @@
         <v>105</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>85</v>
@@ -28117,7 +28129,7 @@
         <v>85</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>85</v>
@@ -28125,10 +28137,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28154,10 +28166,10 @@
         <v>107</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -28172,7 +28184,7 @@
         <v>85</v>
       </c>
       <c r="T214" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="U214" t="s" s="2">
         <v>85</v>
@@ -28208,7 +28220,7 @@
         <v>85</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>83</v>
@@ -28223,7 +28235,7 @@
         <v>105</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>85</v>
@@ -28232,7 +28244,7 @@
         <v>85</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>85</v>
@@ -28240,14 +28252,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -28269,10 +28281,10 @@
         <v>107</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -28287,7 +28299,7 @@
         <v>85</v>
       </c>
       <c r="T215" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="U215" t="s" s="2">
         <v>85</v>
@@ -28323,7 +28335,7 @@
         <v>85</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>83</v>
@@ -28338,7 +28350,7 @@
         <v>105</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>85</v>
@@ -28347,7 +28359,7 @@
         <v>85</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>85</v>
@@ -28355,14 +28367,14 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
@@ -28384,13 +28396,13 @@
         <v>107</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -28404,7 +28416,7 @@
         <v>85</v>
       </c>
       <c r="T216" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="U216" t="s" s="2">
         <v>85</v>
@@ -28420,7 +28432,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>85</v>
@@ -28438,7 +28450,7 @@
         <v>85</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>83</v>
@@ -28453,7 +28465,7 @@
         <v>105</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>85</v>
@@ -28462,7 +28474,7 @@
         <v>85</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>85</v>
@@ -28470,14 +28482,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -28499,10 +28511,10 @@
         <v>107</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -28533,7 +28545,7 @@
       </c>
       <c r="Y217" s="2"/>
       <c r="Z217" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>85</v>
@@ -28551,7 +28563,7 @@
         <v>85</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>83</v>
@@ -28566,7 +28578,7 @@
         <v>105</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>85</v>
@@ -28575,7 +28587,7 @@
         <v>85</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>85</v>
@@ -28583,14 +28595,14 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
@@ -28612,10 +28624,10 @@
         <v>107</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28630,7 +28642,7 @@
         <v>85</v>
       </c>
       <c r="T218" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="U218" t="s" s="2">
         <v>85</v>
@@ -28666,7 +28678,7 @@
         <v>85</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>83</v>
@@ -28681,7 +28693,7 @@
         <v>105</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>85</v>
@@ -28690,7 +28702,7 @@
         <v>85</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>85</v>
@@ -28698,10 +28710,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28727,13 +28739,13 @@
         <v>107</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -28783,7 +28795,7 @@
         <v>85</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>83</v>
@@ -28798,7 +28810,7 @@
         <v>105</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>85</v>
@@ -28807,7 +28819,7 @@
         <v>85</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>85</v>
@@ -28815,10 +28827,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28844,14 +28856,14 @@
         <v>250</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>85</v>
@@ -28864,7 +28876,7 @@
         <v>85</v>
       </c>
       <c r="T220" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="U220" t="s" s="2">
         <v>85</v>
@@ -28900,7 +28912,7 @@
         <v>85</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>83</v>
@@ -28915,7 +28927,7 @@
         <v>105</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>85</v>
@@ -28924,7 +28936,7 @@
         <v>85</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AO220" t="s" s="2">
         <v>85</v>
@@ -28932,10 +28944,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28961,14 +28973,14 @@
         <v>169</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>85</v>
@@ -28996,28 +29008,28 @@
         <v>217</v>
       </c>
       <c r="Y221" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF221" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="Z221" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="AA221" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB221" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC221" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD221" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE221" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF221" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>83</v>
@@ -29032,7 +29044,7 @@
         <v>105</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>111</v>
@@ -29041,7 +29053,7 @@
         <v>85</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>85</v>
@@ -29049,10 +29061,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29078,14 +29090,14 @@
         <v>257</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>85</v>
@@ -29134,7 +29146,7 @@
         <v>85</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>83</v>
@@ -29143,13 +29155,13 @@
         <v>93</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>111</v>
@@ -29158,7 +29170,7 @@
         <v>85</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>85</v>
@@ -29166,10 +29178,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29195,10 +29207,10 @@
         <v>250</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29249,7 +29261,7 @@
         <v>85</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>83</v>
@@ -29264,7 +29276,7 @@
         <v>105</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="AL223" t="s" s="2">
         <v>111</v>
@@ -29281,10 +29293,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29307,19 +29319,19 @@
         <v>85</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>85</v>
@@ -29368,7 +29380,7 @@
         <v>85</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>83</v>
@@ -29383,10 +29395,10 @@
         <v>105</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>85</v>
@@ -29400,10 +29412,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29515,10 +29527,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29632,14 +29644,14 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
@@ -29661,16 +29673,16 @@
         <v>114</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>85</v>
@@ -29719,7 +29731,7 @@
         <v>85</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>83</v>
@@ -29751,10 +29763,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29780,16 +29792,16 @@
         <v>223</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>85</v>
@@ -29838,7 +29850,7 @@
         <v>85</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>93</v>
@@ -29853,16 +29865,16 @@
         <v>105</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>85</v>
@@ -29870,10 +29882,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29899,16 +29911,16 @@
         <v>327</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>85</v>
@@ -29957,7 +29969,7 @@
         <v>85</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>83</v>
@@ -29972,16 +29984,16 @@
         <v>105</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="AM229" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>85</v>
@@ -29989,14 +30001,14 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
@@ -30015,16 +30027,16 @@
         <v>85</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -30074,7 +30086,7 @@
         <v>85</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>83</v>
@@ -30089,7 +30101,7 @@
         <v>105</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="AL230" t="s" s="2">
         <v>111</v>
@@ -30098,7 +30110,7 @@
         <v>85</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>85</v>
@@ -30106,10 +30118,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30135,16 +30147,16 @@
         <v>257</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>85</v>
@@ -30193,7 +30205,7 @@
         <v>85</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>83</v>
@@ -30208,10 +30220,10 @@
         <v>105</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="AL231" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="AM231" t="s" s="2">
         <v>85</v>
@@ -30225,10 +30237,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30251,19 +30263,19 @@
         <v>94</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>85</v>
@@ -30312,7 +30324,7 @@
         <v>85</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>83</v>
@@ -30327,7 +30339,7 @@
         <v>105</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="AL232" t="s" s="2">
         <v>111</v>
@@ -30344,10 +30356,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30459,10 +30471,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30576,10 +30588,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30659,7 +30671,7 @@
         <v>85</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>83</v>
@@ -30691,10 +30703,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30717,16 +30729,16 @@
         <v>94</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
@@ -30776,7 +30788,7 @@
         <v>85</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>93</v>
@@ -30800,7 +30812,7 @@
         <v>85</v>
       </c>
       <c r="AN236" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="AO236" t="s" s="2">
         <v>85</v>
@@ -30808,10 +30820,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30837,10 +30849,10 @@
         <v>169</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -30870,10 +30882,10 @@
         <v>217</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>85</v>
@@ -30891,7 +30903,7 @@
         <v>85</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>93</v>
@@ -30906,7 +30918,7 @@
         <v>105</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="AL237" t="s" s="2">
         <v>111</v>

--- a/StructureDefinition-ng-patient.xlsx
+++ b/StructureDefinition-ng-patient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T07:55:48+01:00</t>
+    <t>2026-08-17T13:27:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ng-patient.xlsx
+++ b/StructureDefinition-ng-patient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T13:27:53+01:00</t>
+    <t>2026-08-17T16:10:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ng-patient.xlsx
+++ b/StructureDefinition-ng-patient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T06:18:50+01:00</t>
+    <t>2026-08-18T15:57:17+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ng-patient.xlsx
+++ b/StructureDefinition-ng-patient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:57:17+01:00</t>
+    <t>2026-08-18T16:47:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
